--- a/Cenário em Ponte/Cromossomo NT/Resultados/Txt/Resultados Parametros/GA/resultados_parametros_pop_5.xlsx
+++ b/Cenário em Ponte/Cromossomo NT/Resultados/Txt/Resultados Parametros/GA/resultados_parametros_pop_5.xlsx
@@ -456,22 +456,22 @@
         <v>0.01</v>
       </c>
       <c r="B2" s="2" t="n">
-        <v>0.982751</v>
+        <v>0.960597</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>0.982751</v>
+        <v>0.960597</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>0.984226</v>
+        <v>0.960597</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>0.984423</v>
+        <v>0.960597</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>0.984423</v>
+        <v>0.964062</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>0.984816</v>
+        <v>0.960597</v>
       </c>
     </row>
     <row r="3">
@@ -479,22 +479,22 @@
         <v>0.05</v>
       </c>
       <c r="B3" s="2" t="n">
-        <v>0.993521</v>
+        <v>0.986098</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>0.986196</v>
+        <v>0.984915</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>0.99372</v>
+        <v>0.987677</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>0.993919</v>
+        <v>0.983537</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>0.99372</v>
+        <v>0.983635</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>0.984816</v>
+        <v>0.996207</v>
       </c>
     </row>
     <row r="4">
@@ -502,22 +502,22 @@
         <v>0.08</v>
       </c>
       <c r="B4" s="2" t="n">
-        <v>0.9953109999999999</v>
+        <v>0.996108</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>0.993919</v>
+        <v>0.996108</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>0.994913</v>
+        <v>0.995112</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>0.993919</v>
+        <v>0.996108</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>0.994416</v>
+        <v>0.995411</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>0.990446</v>
+        <v>0.996108</v>
       </c>
     </row>
     <row r="5">
@@ -525,22 +525,22 @@
         <v>0.1</v>
       </c>
       <c r="B5" s="2" t="n">
-        <v>0.993521</v>
+        <v>0.995012</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>0.993124</v>
+        <v>0.996108</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>0.993521</v>
+        <v>0.98521</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>0.993919</v>
+        <v>0.996207</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>0.994714</v>
+        <v>0.9963070000000001</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>0.988072</v>
+        <v>0.9963070000000001</v>
       </c>
     </row>
     <row r="6"/>

--- a/Cenário em Ponte/Cromossomo NT/Resultados/Txt/Resultados Parametros/GA/resultados_parametros_pop_5.xlsx
+++ b/Cenário em Ponte/Cromossomo NT/Resultados/Txt/Resultados Parametros/GA/resultados_parametros_pop_5.xlsx
@@ -456,22 +456,22 @@
         <v>0.01</v>
       </c>
       <c r="B2" s="2" t="n">
-        <v>0.982063</v>
+        <v>0.994416</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>0.9804929999999999</v>
+        <v>0.995709</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>0.984915</v>
+        <v>0.9953109999999999</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>0.985013</v>
+        <v>0.995709</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>0.985408</v>
+        <v>0.995709</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>0.985408</v>
+        <v>0.995709</v>
       </c>
     </row>
     <row r="3">
@@ -479,22 +479,22 @@
         <v>0.05</v>
       </c>
       <c r="B3" s="2" t="n">
-        <v>0.982063</v>
+        <v>0.995709</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>0.985408</v>
+        <v>0.995709</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>0.985408</v>
+        <v>0.995709</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>0.985408</v>
+        <v>0.995709</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>0.985408</v>
+        <v>0.996207</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>0.985408</v>
+        <v>0.9963070000000001</v>
       </c>
     </row>
     <row r="4">
@@ -502,22 +502,22 @@
         <v>0.08</v>
       </c>
       <c r="B4" s="2" t="n">
-        <v>0.9804929999999999</v>
+        <v>0.994515</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>0.985408</v>
+        <v>0.996506</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>0.984915</v>
+        <v>0.995709</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>0.985408</v>
+        <v>0.995709</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>0.985408</v>
+        <v>0.995709</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>0.985408</v>
+        <v>0.9958090000000001</v>
       </c>
     </row>
     <row r="5">
@@ -525,22 +525,22 @@
         <v>0.1</v>
       </c>
       <c r="B5" s="2" t="n">
-        <v>0.985408</v>
+        <v>0.995709</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>0.985013</v>
+        <v>0.996108</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>0.985408</v>
+        <v>0.995709</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>0.984915</v>
+        <v>0.996207</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>0.985408</v>
+        <v>0.996705</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>0.985408</v>
+        <v>0.996506</v>
       </c>
     </row>
     <row r="6"/>

--- a/Cenário em Ponte/Cromossomo NT/Resultados/Txt/Resultados Parametros/GA/resultados_parametros_pop_5.xlsx
+++ b/Cenário em Ponte/Cromossomo NT/Resultados/Txt/Resultados Parametros/GA/resultados_parametros_pop_5.xlsx
@@ -428,122 +428,112 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H6"/>
+  <dimension ref="A1:B11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="B1" s="1" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="C1" s="1" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="D1" s="1" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="E1" s="1" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="F1" s="1" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="G1" s="1" t="n">
-        <v>0.2</v>
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Combinação de Parâmetros</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Confiabilidade</t>
+        </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
-        <v>0.01</v>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>0.001, 0.9</t>
+        </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>0.994416</v>
-      </c>
-      <c r="C2" s="2" t="n">
-        <v>0.995709</v>
-      </c>
-      <c r="D2" s="2" t="n">
-        <v>0.9953109999999999</v>
-      </c>
-      <c r="E2" s="2" t="n">
-        <v>0.995709</v>
-      </c>
-      <c r="F2" s="2" t="n">
-        <v>0.995709</v>
-      </c>
-      <c r="G2" s="2" t="n">
-        <v>0.995709</v>
+        <v>0.990688</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
-        <v>0.05</v>
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>0.01, 0.8</t>
+        </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>0.995709</v>
-      </c>
-      <c r="C3" s="2" t="n">
-        <v>0.995709</v>
-      </c>
-      <c r="D3" s="2" t="n">
-        <v>0.995709</v>
-      </c>
-      <c r="E3" s="2" t="n">
-        <v>0.995709</v>
-      </c>
-      <c r="F3" s="2" t="n">
-        <v>0.996207</v>
-      </c>
-      <c r="G3" s="2" t="n">
-        <v>0.9963070000000001</v>
+        <v>0.992073</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
-        <v>0.08</v>
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>0.05, 0.7</t>
+        </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>0.994515</v>
-      </c>
-      <c r="C4" s="2" t="n">
-        <v>0.996506</v>
-      </c>
-      <c r="D4" s="2" t="n">
-        <v>0.995709</v>
-      </c>
-      <c r="E4" s="2" t="n">
-        <v>0.995709</v>
-      </c>
-      <c r="F4" s="2" t="n">
-        <v>0.995709</v>
-      </c>
-      <c r="G4" s="2" t="n">
-        <v>0.9958090000000001</v>
+        <v>0.9909249999999999</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
-        <v>0.1</v>
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>0.02, 0.85</t>
+        </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>0.995709</v>
-      </c>
-      <c r="C5" s="2" t="n">
-        <v>0.996108</v>
-      </c>
-      <c r="D5" s="2" t="n">
-        <v>0.995709</v>
-      </c>
-      <c r="E5" s="2" t="n">
-        <v>0.996207</v>
-      </c>
-      <c r="F5" s="2" t="n">
-        <v>0.996705</v>
-      </c>
-      <c r="G5" s="2" t="n">
-        <v>0.996506</v>
-      </c>
-    </row>
-    <row r="6"/>
+        <v>0.99303</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>0.03, 0.75</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="n">
+        <v>0.99232</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>0.008, 0.65</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="n">
+        <v>0.992066</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>0.04, 0.95</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="n">
+        <v>0.991048</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>0.015, 0.6</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="n">
+        <v>0.992066</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>0.025, 0.88</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="n">
+        <v>0.991939</v>
+      </c>
+    </row>
+    <row r="11"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
